--- a/Section_Notes.xlsx
+++ b/Section_Notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/quinnmackay/Documents/GitHub/BICC_Holocene_LayerCount/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/quinnmackay/Library/Mobile Documents/com~apple~CloudDocs/Programming/GitHub/BICC_Holocene_LayerCount/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C482CB0F-B754-0440-B7AE-195B8417AC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FB9584-1589-D649-8A2F-13AC7CAAB2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30240" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24260" yWindow="10000" windowWidth="27780" windowHeight="17620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="191">
   <si>
     <t>EDML m</t>
   </si>
@@ -324,6 +324,288 @@
   </si>
   <si>
     <t>Another really hard one. Dropped uncertain at 337.7, dropped full at 337.85, 336.55. Added to WDC at 1057.9 and 1058.15.</t>
+  </si>
+  <si>
+    <t>Added uncertain at EDML ~615.65. Moved weak uncertain from 616.55 to 616.25 (approx). Might have the exact one wrong.</t>
+  </si>
+  <si>
+    <t>Just after 611.7, merged a fuell and uncertain into one tiepoint</t>
+  </si>
+  <si>
+    <t>Dropped uncertains at 611.23 and 610.88.</t>
+  </si>
+  <si>
+    <t>Removed WDC tp at 1807.9, added one just prior and after (1807.8 and 1808.95)</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Dropedd 607.75</t>
+  </si>
+  <si>
+    <t>Dropped uncertain at 604.9X and 605.8</t>
+  </si>
+  <si>
+    <t>Uncertain added at 604.58</t>
+  </si>
+  <si>
+    <t>Moved leftmost layer on WDC within the bounds</t>
+  </si>
+  <si>
+    <t>Cut uncertains @ 601.35, 600.7, and 602.48</t>
+  </si>
+  <si>
+    <t>Dropped 596.38</t>
+  </si>
+  <si>
+    <t>Dropped 594.1, 594.55, 594.4, 593.65</t>
+  </si>
+  <si>
+    <t>Dropped 589.28, dropped full at 589.1, dropped partial at 588.61, moved the full to the right of it a bit to the left</t>
+  </si>
+  <si>
+    <t>Added partials at 584.45, 585.1, 583.6, 587.2, 585.05. Removed 2 WDC layers around 1748.8 and made one.</t>
+  </si>
+  <si>
+    <t>Added uncertain at 583.02</t>
+  </si>
+  <si>
+    <t>Dropped uncertain at 582.65</t>
+  </si>
+  <si>
+    <t>Uncertain at 578.5, 579.49</t>
+  </si>
+  <si>
+    <t>Uncertain at 577.6. Split 577.85 into two uncertains, 578.23, 577.76</t>
+  </si>
+  <si>
+    <t>WDC uncertain at 1728.9</t>
+  </si>
+  <si>
+    <t>Adjusted left side WDC year to just inside</t>
+  </si>
+  <si>
+    <t>Uncertain WDC at 1726.45, 1726.7. EDC: two layers around 575.95 combined into one</t>
+  </si>
+  <si>
+    <t>Dropped uncertain at 575.23</t>
+  </si>
+  <si>
+    <t>570.7, dropped uncertain and moved full tad left</t>
+  </si>
+  <si>
+    <t>Uncertain added at 567.6</t>
+  </si>
+  <si>
+    <t>uncertain WDC 1707.58</t>
+  </si>
+  <si>
+    <t>added uncertain at 566.24 and 566.35</t>
+  </si>
+  <si>
+    <t>added uncertain at 565.39, 565.08, shifted the full to the right of it a tad more right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dropped uncertain at 561.3, made no data section 561.8-.9 into 2, dropped uncertain 561.19, 562.65, 564.25, </t>
+  </si>
+  <si>
+    <t>558.76 uncertain</t>
+  </si>
+  <si>
+    <t>Flat section before 558 reduced to 2 (from 3). Dropped 558.3, 556.95, 558.3, 558.25</t>
+  </si>
+  <si>
+    <t>added uncertain at 555.25</t>
+  </si>
+  <si>
+    <t>Dead section reduction just prior to 553 by 1. Moved WDC on left just inside. Dropped uncertain at 553.8. Added uncertain to WDC at 1675.8</t>
+  </si>
+  <si>
+    <t>552.43 drop uncertain</t>
+  </si>
+  <si>
+    <t>550.95 add uncertain</t>
+  </si>
+  <si>
+    <t>Dropped uncertain 549.6, 2 reduction in blank section below 546.5</t>
+  </si>
+  <si>
+    <t>Added uncertain at 545.75</t>
+  </si>
+  <si>
+    <t>Dropped all potential from EDML (543.75, 544.25, 544.3, 544.55, 545.23). Dropped a full at 544.2 and 545.1. Added full to WDC at 1655.48</t>
+  </si>
+  <si>
+    <t>Added one to EDML at 543.53</t>
+  </si>
+  <si>
+    <t>Added potential at 542.35, 541.15</t>
+  </si>
+  <si>
+    <t>Drop 538, 539.8, 538.3, 537.2, 536</t>
+  </si>
+  <si>
+    <t>Dropped 535.53</t>
+  </si>
+  <si>
+    <t>Dropped 534.62</t>
+  </si>
+  <si>
+    <t>Added one 533.77</t>
+  </si>
+  <si>
+    <t>Dropped 532.43, 533.25</t>
+  </si>
+  <si>
+    <t>Dropped 531.22</t>
+  </si>
+  <si>
+    <t>Added 530.15</t>
+  </si>
+  <si>
+    <t>Added 529.02</t>
+  </si>
+  <si>
+    <t>Moved left side just in</t>
+  </si>
+  <si>
+    <t>Added one 527.76, 528.03, 527.98</t>
+  </si>
+  <si>
+    <t>Dropped 526.9, added 1611.52 on WDC</t>
+  </si>
+  <si>
+    <t>Dropped 526, 526.15, 526.08, 526.4, 526.5</t>
+  </si>
+  <si>
+    <t>Added 525.3</t>
+  </si>
+  <si>
+    <t>dropped 522.41</t>
+  </si>
+  <si>
+    <t>Dropped 521.73</t>
+  </si>
+  <si>
+    <t>Leaving alone +1/-1 (1)</t>
+  </si>
+  <si>
+    <t>Dropped 521.2, +1/-1 (1)</t>
+  </si>
+  <si>
+    <t>Dropped 518.2, 517.9, 517.8</t>
+  </si>
+  <si>
+    <t>Added 517.1</t>
+  </si>
+  <si>
+    <t>Dropped 514.9, moved L WDC just inside</t>
+  </si>
+  <si>
+    <t>Added 514, 514.27</t>
+  </si>
+  <si>
+    <t>Added 513.36</t>
+  </si>
+  <si>
+    <t>Added 512.87 (v uncertain)</t>
+  </si>
+  <si>
+    <t>Removed 2 added 1 at 512.18</t>
+  </si>
+  <si>
+    <t>Added at 508.6 (2 of them) and 508.3</t>
+  </si>
+  <si>
+    <t>Removed 507.81, 507.93</t>
+  </si>
+  <si>
+    <t>Cut: 493.82, 429.97, 494.2, 495.4, 496.08, 495.57, 496.6, 497.86, 498.26, 499.95, 500.2, 501,02, 500.65, 502.03, 502.27, 501.54, 503.15, 502.93, 503.46, 503.55, 504.83, 505.78, 507.35, 493.83, 506.55</t>
+  </si>
+  <si>
+    <t>Cut: 477.15, 477.52, 478.32, 479.43, 479.65, 479.81, 480.5, 481.5, 481.25, 482.35, 482.75, 483.02, 484.27, 485.59, 486.05, 488.05, 490.3, 493.15, 493.5, 493.25, 478.45, 479, 480.03, 480.45, 480.62, 480.22, 481.39, 482.83, 482.46, 484.27, 483,67, 485.3, 487.57, 487.82, 477.33, 478.53, 478.65, 478.95, 480.57, 480.65, 481.78, 481.5, 482.43, 484.78, 484.9, 491.15</t>
+  </si>
+  <si>
+    <t>Cut: 475.15, 474.2, 474.8, 476.6</t>
+  </si>
+  <si>
+    <t>Cut: 470.7, 470.95, 471.4, 472.08, 473.4, 471.93, 472.8, 472.75, 469.75, 470.53, 472.49, 472.98, 473.1, 473.95, 472.95, 472.85, 470, 470.85, 471.2</t>
+  </si>
+  <si>
+    <t>Cut: 468.3, 467.35, 470.6, 468.25, 467.3</t>
+  </si>
+  <si>
+    <t>Cut: 459.48, 460.4, 462.83, 462, 463.25, 465.32, 465.45, 465.85, 467, 459.9, 462.17, 463.45, 2x around 464.9, 465.5, 466.21</t>
+  </si>
+  <si>
+    <t>Cut: 449.18, 449.7, 451.23, 450.62,450.97, 453.22, 452.97. 455.05, 2x around 456.5, 458.5, 458.1</t>
+  </si>
+  <si>
+    <t>Cute: 447.99</t>
+  </si>
+  <si>
+    <t>Cute: 440.45</t>
+  </si>
+  <si>
+    <t>Add: 437.72, 438.9</t>
+  </si>
+  <si>
+    <t>Cut:1358.2. Add: 435.2, 437.2, 431.3</t>
+  </si>
+  <si>
+    <t>1 into 2 at 430.7</t>
+  </si>
+  <si>
+    <t>Added at 429.16</t>
+  </si>
+  <si>
+    <t>Cut: 421.21, 422.3, 422.7, 422.43, 423.03, 423.37, 423.78, 452.21, 426.7, (2 into 1) 427.55, 428.65, 428.9, 428.52</t>
+  </si>
+  <si>
+    <t>419.92, 4 around 418, 418.4, 419.9, 420.6, 420.7, 418.2, 419.45, 419.8</t>
+  </si>
+  <si>
+    <t>Add 417.05</t>
+  </si>
+  <si>
+    <t>Cut: 411.05, 410.95, 410.45, 409.65, 411.9</t>
+  </si>
+  <si>
+    <t>Cut: 399.5, 401.9, 403.75, 404.2, 404.7, 406.43, 408.25, 408.7, 409.08, 409.22</t>
+  </si>
+  <si>
+    <t>Cut: 398.55, 396.5</t>
+  </si>
+  <si>
+    <t>Cut 392.8</t>
+  </si>
+  <si>
+    <t>Cut 392.38</t>
+  </si>
+  <si>
+    <t>Dropped 3 after 385, 387.05, 389, 390.3, 391.2</t>
+  </si>
+  <si>
+    <t>381.65, 381.1, 380.7, 380.8</t>
+  </si>
+  <si>
+    <t>Cut: 374.9, 373.6, 376.3</t>
+  </si>
+  <si>
+    <t>Cut: 366.9, 367, 367.1, 365, 369.65, 365.2, 367.2, 369.5</t>
+  </si>
+  <si>
+    <t>Reduce 1 past 362, 362.52, 363.48</t>
+  </si>
+  <si>
+    <t>Cut: 358.3, 361.2, remove one around 361, 357.4, 358, 357.05</t>
+  </si>
+  <si>
+    <t>Cut: 351.15, 350.65, 351.85, remove 2 around 354.7, 355.1, 352.05, 349.75, 352.1, 354.4, 355.9, 352.5</t>
+  </si>
+  <si>
+    <t>339.7, 340.05, 340.58, 340.13, 340.9, 343.25, 343.95, 345.35, 345.65, 346.2, 347.25, 348.45, 348.54, 348.62, 348.8, 348.86, 339.6, 341.92, 342.56, 343.55, 346.7, 349.6, 340.4</t>
   </si>
 </sst>
 </file>
@@ -404,7 +686,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -414,6 +696,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -767,9 +1050,6 @@
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
@@ -1682,7 +1962,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="4">
+      <c r="A38">
         <v>37</v>
       </c>
       <c r="B38">
@@ -1708,7 +1988,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="4">
+      <c r="A39">
         <v>38</v>
       </c>
       <c r="B39">
@@ -1734,7 +2014,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="4">
+      <c r="A40">
         <v>39</v>
       </c>
       <c r="B40">
@@ -1760,7 +2040,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="4">
+      <c r="A41">
         <v>40</v>
       </c>
       <c r="B41">
@@ -1786,7 +2066,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="4">
+      <c r="A42">
         <v>41</v>
       </c>
       <c r="B42">
@@ -1812,7 +2092,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="4">
+      <c r="A43">
         <v>42</v>
       </c>
       <c r="B43">
@@ -1838,7 +2118,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="4">
+      <c r="A44">
         <v>43</v>
       </c>
       <c r="B44">
@@ -1864,7 +2144,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="4">
+      <c r="A45">
         <v>44</v>
       </c>
       <c r="B45">
@@ -1890,7 +2170,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="4">
+      <c r="A46">
         <v>45</v>
       </c>
       <c r="B46">
@@ -1916,7 +2196,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="4">
+      <c r="A47">
         <v>46</v>
       </c>
       <c r="B47">
@@ -1942,7 +2222,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="4">
+      <c r="A48">
         <v>47</v>
       </c>
       <c r="B48">
@@ -1968,7 +2248,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="4">
+      <c r="A49">
         <v>48</v>
       </c>
       <c r="B49">
@@ -1994,7 +2274,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="4">
+      <c r="A50">
         <v>49</v>
       </c>
       <c r="B50">
@@ -2020,7 +2300,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="4">
+      <c r="A51">
         <v>50</v>
       </c>
       <c r="B51">
@@ -2046,7 +2326,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="4">
+      <c r="A52">
         <v>51</v>
       </c>
       <c r="B52">
@@ -2072,7 +2352,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" s="4">
+      <c r="A53">
         <v>52</v>
       </c>
       <c r="B53">
@@ -2098,7 +2378,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="4">
+      <c r="A54">
         <v>53</v>
       </c>
       <c r="B54">
@@ -2124,7 +2404,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" s="4">
+      <c r="A55">
         <v>54</v>
       </c>
       <c r="B55">
@@ -2150,7 +2430,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="4">
+      <c r="A56">
         <v>55</v>
       </c>
       <c r="B56">
@@ -2176,7 +2456,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="4">
+      <c r="A57">
         <v>56</v>
       </c>
       <c r="B57">
@@ -2202,7 +2482,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="4">
+      <c r="A58">
         <v>57</v>
       </c>
       <c r="B58">
@@ -2228,7 +2508,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="4">
+      <c r="A59">
         <v>58</v>
       </c>
       <c r="B59">
@@ -2254,7 +2534,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="4">
+      <c r="A60">
         <v>59</v>
       </c>
       <c r="B60">
@@ -2280,7 +2560,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="4">
+      <c r="A61">
         <v>60</v>
       </c>
       <c r="B61">
@@ -2306,7 +2586,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="4">
+      <c r="A62">
         <v>61</v>
       </c>
       <c r="B62">
@@ -2332,7 +2612,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="4">
+      <c r="A63">
         <v>62</v>
       </c>
       <c r="B63">
@@ -2358,7 +2638,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="4">
+      <c r="A64">
         <v>63</v>
       </c>
       <c r="B64">
@@ -2384,7 +2664,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" s="4">
+      <c r="A65">
         <v>64</v>
       </c>
       <c r="B65">
@@ -2410,7 +2690,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66">
+      <c r="A66" s="4">
         <v>65</v>
       </c>
       <c r="B66">
@@ -2431,9 +2711,12 @@
       <c r="G66">
         <v>22.665157008064849</v>
       </c>
+      <c r="H66" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67">
+      <c r="A67" s="4">
         <v>66</v>
       </c>
       <c r="B67">
@@ -2454,9 +2737,12 @@
       <c r="G67">
         <v>12.350105362253091</v>
       </c>
+      <c r="H67" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68">
+      <c r="A68" s="4">
         <v>67</v>
       </c>
       <c r="B68">
@@ -2477,9 +2763,12 @@
       <c r="G68">
         <v>6.459456358135867</v>
       </c>
+      <c r="H68" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69">
+      <c r="A69" s="4">
         <v>68</v>
       </c>
       <c r="B69">
@@ -2500,9 +2789,12 @@
       <c r="G69">
         <v>3.2318920868747232</v>
       </c>
+      <c r="H69" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70">
+      <c r="A70" s="4">
         <v>69</v>
       </c>
       <c r="B70">
@@ -2523,9 +2815,12 @@
       <c r="G70">
         <v>7.6392241042103706</v>
       </c>
+      <c r="H70" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71">
+      <c r="A71" s="4">
         <v>70</v>
       </c>
       <c r="B71">
@@ -2546,9 +2841,12 @@
       <c r="G71">
         <v>3.4019300691097669</v>
       </c>
+      <c r="H71" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72">
+      <c r="A72" s="4">
         <v>71</v>
       </c>
       <c r="B72">
@@ -2569,9 +2867,12 @@
       <c r="G72">
         <v>-6.3959376855564187E-2</v>
       </c>
+      <c r="H72" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73">
+      <c r="A73" s="4">
         <v>72</v>
       </c>
       <c r="B73">
@@ -2592,9 +2893,12 @@
       <c r="G73">
         <v>2.9747550431557102</v>
       </c>
+      <c r="H73" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74">
+      <c r="A74" s="4">
         <v>73</v>
       </c>
       <c r="B74">
@@ -2615,9 +2919,12 @@
       <c r="G74">
         <v>7.7548566821724307</v>
       </c>
+      <c r="H74" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75">
+      <c r="A75" s="4">
         <v>74</v>
       </c>
       <c r="B75">
@@ -2638,9 +2945,12 @@
       <c r="G75">
         <v>0.30416190951928002</v>
       </c>
+      <c r="H75" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76">
+      <c r="A76" s="4">
         <v>75</v>
       </c>
       <c r="B76">
@@ -2661,9 +2971,12 @@
       <c r="G76">
         <v>0.78476532274635247</v>
       </c>
+      <c r="H76" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77">
+      <c r="A77" s="4">
         <v>76</v>
       </c>
       <c r="B77">
@@ -2684,9 +2997,12 @@
       <c r="G77">
         <v>1.3971929666286089</v>
       </c>
+      <c r="H77" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78">
+      <c r="A78" s="4">
         <v>77</v>
       </c>
       <c r="B78">
@@ -2707,9 +3023,12 @@
       <c r="G78">
         <v>1.6020007209972389</v>
       </c>
+      <c r="H78" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79">
+      <c r="A79" s="4">
         <v>78</v>
       </c>
       <c r="B79">
@@ -2730,9 +3049,12 @@
       <c r="G79">
         <v>9.4735812131511921</v>
       </c>
+      <c r="H79" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80">
+      <c r="A80" s="5">
         <v>79</v>
       </c>
       <c r="B80">
@@ -2753,9 +3075,12 @@
       <c r="G80">
         <v>5.1248365868395922</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81">
+      <c r="H80" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" s="5">
         <v>80</v>
       </c>
       <c r="B81">
@@ -2776,9 +3101,12 @@
       <c r="G81">
         <v>-0.14816736901047989</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82">
+      <c r="H81" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" s="5">
         <v>81</v>
       </c>
       <c r="B82">
@@ -2799,9 +3127,12 @@
       <c r="G82">
         <v>12.3428282828263</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83">
+      <c r="H82" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" s="5">
         <v>82</v>
       </c>
       <c r="B83">
@@ -2822,9 +3153,12 @@
       <c r="G83">
         <v>11.97085611358489</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84">
+      <c r="H83" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" s="5">
         <v>83</v>
       </c>
       <c r="B84">
@@ -2845,9 +3179,12 @@
       <c r="G84">
         <v>-0.62990570035981364</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85">
+      <c r="H84" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" s="5">
         <v>84</v>
       </c>
       <c r="B85">
@@ -2868,9 +3205,12 @@
       <c r="G85">
         <v>-0.1473550954970051</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86">
+      <c r="H85" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" s="5">
         <v>85</v>
       </c>
       <c r="B86">
@@ -2891,9 +3231,12 @@
       <c r="G86">
         <v>-1.042409294815116</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87">
+      <c r="H86" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" s="5">
         <v>86</v>
       </c>
       <c r="B87">
@@ -2914,9 +3257,12 @@
       <c r="G87">
         <v>-4.0985334407514529</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88">
+      <c r="H87" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" s="5">
         <v>87</v>
       </c>
       <c r="B88">
@@ -2937,9 +3283,12 @@
       <c r="G88">
         <v>-1.584635459817036</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89">
+      <c r="H88" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" s="5">
         <v>88</v>
       </c>
       <c r="B89">
@@ -2960,9 +3309,12 @@
       <c r="G89">
         <v>0.81726765823623282</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90">
+      <c r="H89" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" s="5">
         <v>89</v>
       </c>
       <c r="B90">
@@ -2983,9 +3335,12 @@
       <c r="G90">
         <v>0.47795101119936589</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A91">
+      <c r="H90" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" s="5">
         <v>90</v>
       </c>
       <c r="B91">
@@ -3006,9 +3361,12 @@
       <c r="G91">
         <v>0.30130031374392269</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92">
+      <c r="H91" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92" s="5">
         <v>91</v>
       </c>
       <c r="B92">
@@ -3029,9 +3387,12 @@
       <c r="G92">
         <v>11.70193809595094</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A93">
+      <c r="H92" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93" s="5">
         <v>92</v>
       </c>
       <c r="B93">
@@ -3052,9 +3413,12 @@
       <c r="G93">
         <v>17.162169643162091</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A94">
+      <c r="H93" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" s="5">
         <v>93</v>
       </c>
       <c r="B94">
@@ -3075,9 +3439,12 @@
       <c r="G94">
         <v>3.98559003079481</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A95">
+      <c r="H94" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95" s="5">
         <v>94</v>
       </c>
       <c r="B95">
@@ -3098,9 +3465,12 @@
       <c r="G95">
         <v>19.839761339881079</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A96">
+      <c r="H95" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" s="5">
         <v>95</v>
       </c>
       <c r="B96">
@@ -3121,9 +3491,12 @@
       <c r="G96">
         <v>3.417433825154149</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A97">
+      <c r="H96" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97" s="5">
         <v>96</v>
       </c>
       <c r="B97">
@@ -3144,8 +3517,11 @@
       <c r="G97">
         <v>44.516004478397008</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H97" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3167,8 +3543,11 @@
       <c r="G98">
         <v>24.686380216262481</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H98" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3190,8 +3569,11 @@
       <c r="G99">
         <v>1.8162620224529751</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H99" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3213,8 +3595,11 @@
       <c r="G100">
         <v>-3.0669276094295128</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H100" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3236,8 +3621,11 @@
       <c r="G101">
         <v>-0.1911770688957404</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H101" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -3259,8 +3647,11 @@
       <c r="G102">
         <v>1.433539534908959</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H102" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -3282,8 +3673,11 @@
       <c r="G103">
         <v>-0.53119688866991055</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H103" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -3305,8 +3699,11 @@
       <c r="G104">
         <v>-0.48042568477922032</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H104" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -3328,8 +3725,11 @@
       <c r="G105">
         <v>-1.7519885580804839</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H105" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -3351,8 +3751,11 @@
       <c r="G106">
         <v>-2.3568037279765122</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H106" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -3374,8 +3777,11 @@
       <c r="G107">
         <v>1.0768059151032501</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H107" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -3397,8 +3803,11 @@
       <c r="G108">
         <v>0.38718923933174659</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H108" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -3420,8 +3829,11 @@
       <c r="G109">
         <v>0.11576758147566581</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H109" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -3443,8 +3855,11 @@
       <c r="G110">
         <v>-0.95194018562779092</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H110" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -3466,8 +3881,11 @@
       <c r="G111">
         <v>3.3193733617272301</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H111" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
@@ -3489,8 +3907,11 @@
       <c r="G112">
         <v>-0.36314847417725099</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H112" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>112</v>
       </c>
@@ -3512,8 +3933,11 @@
       <c r="G113">
         <v>1.3017360221938361</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H113" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>113</v>
       </c>
@@ -3535,8 +3959,11 @@
       <c r="G114">
         <v>1.3486620697203759</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H114" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>114</v>
       </c>
@@ -3558,8 +3985,11 @@
       <c r="G115">
         <v>1.052409473174521</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H115" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>115</v>
       </c>
@@ -3581,8 +4011,11 @@
       <c r="G116">
         <v>0.40125270562657528</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H116" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>116</v>
       </c>
@@ -3604,8 +4037,11 @@
       <c r="G117">
         <v>5.2118929555290379</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H117" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>117</v>
       </c>
@@ -3627,8 +4063,11 @@
       <c r="G118">
         <v>1.4922736118478499</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H118" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>118</v>
       </c>
@@ -3650,8 +4089,11 @@
       <c r="G119">
         <v>0.53584627885356895</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H119" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>119</v>
       </c>
@@ -3673,8 +4115,11 @@
       <c r="G120">
         <v>-2.2318930771089072</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H120" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>120</v>
       </c>
@@ -3696,8 +4141,11 @@
       <c r="G121">
         <v>-1.1743418803434911</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H121" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>121</v>
       </c>
@@ -3719,8 +4167,11 @@
       <c r="G122">
         <v>-0.65944530448359728</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H122" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>122</v>
       </c>
@@ -3742,8 +4193,11 @@
       <c r="G123">
         <v>-1.114202714166822</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H123" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>123</v>
       </c>
@@ -3765,8 +4219,11 @@
       <c r="G124">
         <v>0.884625850341763</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H124" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>124</v>
       </c>
@@ -3788,8 +4245,11 @@
       <c r="G125">
         <v>-1.3367109080718359E-2</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H125" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>125</v>
       </c>
@@ -3811,8 +4271,11 @@
       <c r="G126">
         <v>0.11757459207728969</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H126" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>126</v>
       </c>
@@ -3834,8 +4297,11 @@
       <c r="G127">
         <v>1.6008535353485061</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H127" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>127</v>
       </c>
@@ -3857,8 +4323,11 @@
       <c r="G128">
         <v>0.32099340342392679</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H128" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>128</v>
       </c>
@@ -3880,8 +4349,11 @@
       <c r="G129">
         <v>-0.81391981034903438</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H129" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>129</v>
       </c>
@@ -3903,8 +4375,11 @@
       <c r="G130">
         <v>1.158107959292465</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H130" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>130</v>
       </c>
@@ -3926,8 +4401,11 @@
       <c r="G131">
         <v>0.79364096862082079</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H131" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>131</v>
       </c>
@@ -3949,8 +4427,11 @@
       <c r="G132">
         <v>5.5444499757177246</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H132" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>132</v>
       </c>
@@ -3972,8 +4453,11 @@
       <c r="G133">
         <v>-2.533658906675555</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H133" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>133</v>
       </c>
@@ -3995,8 +4479,11 @@
       <c r="G134">
         <v>-1.2227374481808511</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H134" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>134</v>
       </c>
@@ -4018,8 +4505,11 @@
       <c r="G135">
         <v>7.7251635574721149</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H135" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>135</v>
       </c>
@@ -4041,8 +4531,11 @@
       <c r="G136">
         <v>-3.7019973933638539E-2</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H136" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>136</v>
       </c>
@@ -4064,8 +4557,11 @@
       <c r="G137">
         <v>2.990746803083312</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H137" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>137</v>
       </c>
@@ -4087,8 +4583,11 @@
       <c r="G138">
         <v>-0.1054305483212374</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H138" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>138</v>
       </c>
@@ -4110,8 +4609,11 @@
       <c r="G139">
         <v>-1.335738304549523</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H139" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>139</v>
       </c>
@@ -4133,8 +4635,11 @@
       <c r="G140">
         <v>0.74893838422940462</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H140" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>140</v>
       </c>
@@ -4156,8 +4661,11 @@
       <c r="G141">
         <v>3.2644967227261081</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H141" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>141</v>
       </c>
@@ -4179,8 +4687,11 @@
       <c r="G142">
         <v>-0.86890846242749831</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H142" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>142</v>
       </c>
@@ -4202,8 +4713,11 @@
       <c r="G143">
         <v>4.1337780969006417</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H143" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>143</v>
       </c>
@@ -4225,8 +4739,11 @@
       <c r="G144">
         <v>-0.22092614265602609</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H144" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>144</v>
       </c>
@@ -4248,8 +4765,11 @@
       <c r="G145">
         <v>-3.654895273939474E-3</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H145" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>145</v>
       </c>
@@ -4271,8 +4791,11 @@
       <c r="G146">
         <v>5.3604743392806986</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H146" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>146</v>
       </c>
@@ -4294,8 +4817,11 @@
       <c r="G147">
         <v>-2.3851492537323788</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H147" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>147</v>
       </c>
@@ -4317,8 +4843,11 @@
       <c r="G148">
         <v>-1.399009740258407</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H148" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>148</v>
       </c>
@@ -4340,8 +4869,11 @@
       <c r="G149">
         <v>0.19394775678847509</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H149" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>149</v>
       </c>
@@ -4363,8 +4895,11 @@
       <c r="G150">
         <v>-0.32471074380009668</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H150" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>150</v>
       </c>
@@ -4386,8 +4921,11 @@
       <c r="G151">
         <v>0.52577901657787152</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H151" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>151</v>
       </c>
@@ -4409,8 +4947,11 @@
       <c r="G152">
         <v>0.16269500939597489</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H152" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>152</v>
       </c>
@@ -4432,8 +4973,11 @@
       <c r="G153">
         <v>1.472330642331144</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H153" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>153</v>
       </c>
@@ -4455,8 +4999,11 @@
       <c r="G154">
         <v>2.2295977323210541</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H154" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>154</v>
       </c>
@@ -4478,8 +5025,11 @@
       <c r="G155">
         <v>8.5205223456796375E-2</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H155" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>155</v>
       </c>
@@ -4501,8 +5051,11 @@
       <c r="G156">
         <v>1.993054926570039</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H156" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>156</v>
       </c>
@@ -4524,8 +5077,11 @@
       <c r="G157">
         <v>-4.6114655809542464</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H157" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>157</v>
       </c>
@@ -4547,8 +5103,11 @@
       <c r="G158">
         <v>-1.5873475160842641</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H158" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>158</v>
       </c>
@@ -4570,8 +5129,11 @@
       <c r="G159">
         <v>0.66537781911210914</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H159" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>159</v>
       </c>
@@ -4593,8 +5155,11 @@
       <c r="G160">
         <v>-0.86753993133061158</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H160" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>160</v>
       </c>
@@ -4616,8 +5181,11 @@
       <c r="G161">
         <v>-6.5659827959425456</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H161" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>161</v>
       </c>
@@ -4639,8 +5207,11 @@
       <c r="G162">
         <v>2.667474312089325</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H162" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>162</v>
       </c>
@@ -4662,8 +5233,11 @@
       <c r="G163">
         <v>0.66400419581623282</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H163" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>163</v>
       </c>
@@ -4685,8 +5259,11 @@
       <c r="G164">
         <v>3.227415760866279</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H164" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>164</v>
       </c>
@@ -4708,8 +5285,11 @@
       <c r="G165">
         <v>0.76224106368135836</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H165" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>165</v>
       </c>
@@ -4731,8 +5311,11 @@
       <c r="G166">
         <v>0.64158976724866079</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H166" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>166</v>
       </c>
@@ -4754,8 +5337,11 @@
       <c r="G167">
         <v>4.4561472919667722E-2</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H167" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>167</v>
       </c>
@@ -4777,8 +5363,11 @@
       <c r="G168">
         <v>2.1624482758634258</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H168" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>168</v>
       </c>
@@ -4800,8 +5389,11 @@
       <c r="G169">
         <v>1.338678160920608</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H169" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>169</v>
       </c>
@@ -4823,8 +5415,11 @@
       <c r="G170">
         <v>-1.839091905661917</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H170" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>170</v>
       </c>
@@ -4846,8 +5441,11 @@
       <c r="G171">
         <v>2.63336892681582</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H171" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>171</v>
       </c>
@@ -4869,8 +5467,11 @@
       <c r="G172">
         <v>0.95326368384849047</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H172" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>172</v>
       </c>
@@ -4892,8 +5493,11 @@
       <c r="G173">
         <v>0.29952480936299247</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H173" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>173</v>
       </c>
@@ -4915,8 +5519,11 @@
       <c r="G174">
         <v>2.4373863212404099</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H174" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>174</v>
       </c>
@@ -4938,8 +5545,11 @@
       <c r="G175">
         <v>2.0174255590245589</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H175" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>175</v>
       </c>
@@ -4960,6 +5570,9 @@
       </c>
       <c r="G176">
         <v>0.5983057525663753</v>
+      </c>
+      <c r="H176" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
@@ -4983,6 +5596,9 @@
       </c>
       <c r="G177">
         <v>-0.1822486296114221</v>
+      </c>
+      <c r="H177" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
